--- a/ANEXO 1.4.xlsx
+++ b/ANEXO 1.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Escritorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2501F2AE-93A5-4AE5-98AB-824D16AD6DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17D68A4-FB8E-4D53-8069-A705D712F602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FC060707-C6CA-48E9-9D74-8DDD0D7918A0}"/>
   </bookViews>
@@ -39,64 +39,391 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Clasificación</t>
-  </si>
-  <si>
-    <t>Familias Representativas</t>
-  </si>
-  <si>
-    <t>% del Gasto</t>
-  </si>
-  <si>
-    <t>Ubicación en el Layout (Slotting)</t>
-  </si>
-  <si>
-    <t>Control de Inventario</t>
-  </si>
-  <si>
-    <t>Clase A (Alta rotación)</t>
-  </si>
-  <si>
-    <t>Familia A (Fierro, Cemento Polpaico)</t>
-  </si>
-  <si>
-    <t>A nivel de piso o racks de fácil acceso, inmediatamente adyacentes a muelles de recepción/despacho.</t>
-  </si>
-  <si>
-    <t>Estricto, mediante conteos de frecuencia semanal.</t>
-  </si>
-  <si>
-    <t>Clase B (Rotación media)</t>
-  </si>
-  <si>
-    <t>Familias B y C (Consumibles, eléctricos)</t>
-  </si>
-  <si>
-    <t>Zonas intermedias del Centro de Distribución y bodegas de obra.</t>
-  </si>
-  <si>
-    <t>Frecuencia media de auditoría.</t>
-  </si>
-  <si>
-    <t>Clase C (Baja rotación)</t>
-  </si>
-  <si>
-    <t>Familia F (Aseo, papelería - excluyendo combustibles)</t>
-  </si>
-  <si>
-    <t>Niveles superiores de racks o zonas más profundas/alejadas para no entorpecer el flujo.</t>
-  </si>
-  <si>
-    <t>Conteo esporádico.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Matriz de Diagnóstico y Estructuración Logística (ABC/XYZ)</t>
+  </si>
+  <si>
+    <t>Clasificación ABC</t>
+  </si>
+  <si>
+    <t>Clasificación XYZ (Comportamiento)</t>
+  </si>
+  <si>
+    <t>Familia Logística Asociada</t>
+  </si>
+  <si>
+    <t>% del Gasto Total</t>
+  </si>
+  <si>
+    <t>Nivel de Criticidad Operacional</t>
+  </si>
+  <si>
+    <t>Estrategia de Almacenamiento (Layout propuesto)</t>
+  </si>
+  <si>
+    <t>Estrategia de Control y Revisión</t>
+  </si>
+  <si>
+    <t>Brechas y Hallazgos Críticos en el Caso</t>
+  </si>
+  <si>
+    <t>CLASE A</t>
+  </si>
+  <si>
+    <r>
+      <t>Tipo X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Demanda constante y predecible en obra)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Familia A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Estructurales) y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Familia D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Hidráulicos)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>51%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (42% Fam. A + 9% Fam. D)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Alta Prioridad (Crítica)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Su quiebre paraliza los frentes de trabajo inmediatamente.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zona de Alta Rotación:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A nivel de piso o primer nivel de racks, ubicados estratégicamente cerca de las zonas de recepción y muelles de despacho para optimizar el picking.</t>
+    </r>
+  </si>
+  <si>
+    <t>Control ultra estricto. Revisiones cíclicas frecuentes (semanales) y registro transaccional en tiempo real obligatorio.</t>
+  </si>
+  <si>
+    <r>
+      <t>Colapso operativo:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Concentran los 47 quiebres de stock reportados (31 en Fam. A, 16 en Fam. D). Latencia de 15 días en registros genera "quiebres invisibles" y $312 millones en pérdidas por paralización.</t>
+    </r>
+  </si>
+  <si>
+    <t>CLASE B</t>
+  </si>
+  <si>
+    <r>
+      <t>Tipo Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Demanda con variabilidad moderada)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Familia B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Consumibles) y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Familia C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Eléctricos)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (28% Fam. B + 12% Fam. C)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Prioridad Media</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Artículos de transición; su falta retrasa especialidades pero no detiene la obra estructural.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zona de Transición:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Estanterías selectivas convencionales, buscando un equilibrio técnico entre densidad de almacenamiento y velocidad de acceso razonable.</t>
+    </r>
+  </si>
+  <si>
+    <t>Control moderado. Revisiones periódicas menos frecuentes (quincenales/mensuales).</t>
+  </si>
+  <si>
+    <r>
+      <t>Consumos Fantasmas:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vales manuales no digitalizados a tiempo. Ej: 1.600 metros de cable vulcanizado (Fam. C) consumidos en febrero y no rebajados del WMS, generando stock ficticio.</t>
+    </r>
+  </si>
+  <si>
+    <t>CLASE C</t>
+  </si>
+  <si>
+    <r>
+      <t>Tipo Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Demanda irregular o de baja rotación)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Familia E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Herramientas) y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Familia F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Varios / Insumos Generales)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (6% Fam. E + 3% Fam. F)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Baja Prioridad</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Alta cantidad de códigos (SKU) pero bajo impacto financiero global.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zona de Máxima Densificación:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Niveles superiores de los racks o en los sectores más alejados de los muelles de expedición, liberando el espacio vital.</t>
+    </r>
+  </si>
+  <si>
+    <t>Control básico. Compras en grandes volúmenes para asegurar stock a largo plazo y evitar sobrecostos administrativos.</t>
+  </si>
+  <si>
+    <r>
+      <t>Falla de Seguridad / HAZMAT:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> La Familia F mezcla erróneamente artículos de papelería con Petróleo Grado 2, vulnerando el principio de segregación para mercancías peligrosas e inflamables.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,17 +432,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -127,12 +449,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -141,62 +463,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -204,22 +481,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,82 +829,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83CDEE5E-E08B-44E4-8AA8-C0B396891072}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="46.21875" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="4" max="4" width="40.109375" customWidth="1"/>
     <col min="5" max="5" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.21875" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" customWidth="1"/>
+    <col min="8" max="8" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.42</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
+    <row r="3" spans="1:8" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
+    <row r="4" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
+    <row r="5" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
